--- a/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536302_LIGAREGULARB_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536302_LIGAREGULARB_PROCESSED.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y27"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1870,7 +1870,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. BAH</t>
+          <t>K. BAOKO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1882,67 +1882,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8012</v>
+        <v>1.189</v>
       </c>
       <c r="E18" t="n">
-        <v>2.5846</v>
+        <v>1.364</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.7835</v>
+        <v>-0.175</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.5116</v>
+        <v>1.5885</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0513</v>
+        <v>1.5261</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.4603</v>
+        <v>0.0624</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4134</v>
+        <v>3.125</v>
       </c>
       <c r="K18" t="n">
-        <v>1.2162</v>
+        <v>2.3359</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1973</v>
+        <v>0.789</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.925</v>
+        <v>-1.5365</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2674</v>
+        <v>-0.8099</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.6575</v>
+        <v>-0.7266</v>
       </c>
       <c r="P18" t="n">
-        <v>1.8493</v>
+        <v>-2.6713</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-4.1096</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8493</v>
+        <v>1.4384</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2716</v>
+        <v>1.3334</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6918</v>
+        <v>1.2801</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4201</v>
+        <v>0.0533</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1918</v>
+        <v>0.9384</v>
       </c>
       <c r="W18" t="n">
-        <v>0.4794</v>
+        <v>1.0685</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2877</v>
+        <v>-0.1301</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. BAOKO</t>
+          <t>D. BAH</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1965,67 +1965,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5972</v>
+        <v>0.8012</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7722</v>
+        <v>2.5846</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.175</v>
+        <v>-1.7835</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9967</v>
+        <v>-1.5116</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5261</v>
+        <v>-0.0513</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5293</v>
+        <v>-1.4603</v>
       </c>
       <c r="J19" t="n">
-        <v>2.5332</v>
+        <v>1.4134</v>
       </c>
       <c r="K19" t="n">
-        <v>2.3359</v>
+        <v>1.2162</v>
       </c>
       <c r="L19" t="n">
         <v>0.1973</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5365</v>
+        <v>-2.925</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8099</v>
+        <v>-1.2674</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7266</v>
+        <v>-1.6575</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.6713</v>
+        <v>1.8493</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.1096</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4384</v>
+        <v>1.8493</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3334</v>
+        <v>0.2716</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2801</v>
+        <v>0.6918</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0533</v>
+        <v>-0.4201</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9384</v>
+        <v>0.1918</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0685</v>
+        <v>0.4794</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1301</v>
+        <v>-0.2877</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K.  BAOKO</t>
+          <t>D. CEBOLLA PORCAR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2048,67 +2048,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5918</v>
+        <v>0.0094</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5918</v>
+        <v>0.2811</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>-0.2717</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5918</v>
+        <v>-1.8158</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>-4.0717</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5918</v>
+        <v>2.2558</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5918</v>
+        <v>0.3782</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>-2.8568</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5918</v>
+        <v>3.2351</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>-2.194</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>-1.2148</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.411</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.0274</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.4384</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>0.2361</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>0.4508</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>-0.2147</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.1781</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.4794</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.6986</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. CEBOLLA PORCAR</t>
+          <t>D. LOZANO GIMENEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2131,67 +2131,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0094</v>
+        <v>-0.6875</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2811</v>
+        <v>0.1064</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2717</v>
+        <v>-0.794</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.8158</v>
+        <v>-0.8416</v>
       </c>
       <c r="H21" t="n">
-        <v>-4.0717</v>
+        <v>-0.1945</v>
       </c>
       <c r="I21" t="n">
-        <v>2.2558</v>
+        <v>-0.6471</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3782</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.8568</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>3.2351</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.194</v>
+        <v>-0.8416</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2148</v>
+        <v>-0.1945</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9792</v>
+        <v>-0.6471</v>
       </c>
       <c r="P21" t="n">
-        <v>0.411</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0274</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4384</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2361</v>
+        <v>0.1541</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4508</v>
+        <v>0.1064</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2147</v>
+        <v>0.0477</v>
       </c>
       <c r="V21" t="n">
-        <v>1.1781</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.4794</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.6986</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. LOZANO GIMENEZ</t>
+          <t>J. FANER CATALA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2214,67 +2214,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6875</v>
+        <v>-2.1082</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1064</v>
+        <v>-0.313</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.794</v>
+        <v>-1.7952</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.8416</v>
+        <v>0.2639</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1945</v>
+        <v>-0.1176</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6471</v>
+        <v>0.3815</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>3.8618</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1.9646</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.8971</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8416</v>
+        <v>-3.5978</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1945</v>
+        <v>-2.0822</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6471</v>
+        <v>-1.5156</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-1.2329</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-4.1096</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.8767</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1541</v>
+        <v>-0.5023</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1064</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0477</v>
+        <v>-0.4372</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.637</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.637</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. FANER CATALA</t>
+          <t>H. ARBOSA ROLDAN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2297,67 +2297,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.1082</v>
+        <v>-2.1403</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.313</v>
+        <v>0.5755</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7952</v>
+        <v>-2.7158</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2639</v>
+        <v>-1.4874</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1176</v>
+        <v>-1.8342</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3815</v>
+        <v>0.3468</v>
       </c>
       <c r="J23" t="n">
-        <v>3.8618</v>
+        <v>1.7685</v>
       </c>
       <c r="K23" t="n">
-        <v>1.9646</v>
+        <v>-0.1251</v>
       </c>
       <c r="L23" t="n">
-        <v>1.8971</v>
+        <v>1.8937</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.5978</v>
+        <v>-3.2559</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.0822</v>
+        <v>-1.7091</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.5156</v>
+        <v>-1.5469</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.2329</v>
+        <v>-0.411</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.1096</v>
+        <v>-2.0548</v>
       </c>
       <c r="R23" t="n">
-        <v>2.8767</v>
+        <v>1.6439</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5023</v>
+        <v>-0.0022</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.06510000000000001</v>
+        <v>0.8618</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4372</v>
+        <v>-0.864</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.637</v>
+        <v>-0.2397</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.637</v>
+        <v>-0.2397</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>H. ARBOSA ROLDAN</t>
+          <t>R. DIAZ DEL VALLE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2380,67 +2380,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.1403</v>
+        <v>-2.2009</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5755</v>
+        <v>-3.3037</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.7158</v>
+        <v>1.1028</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.4874</v>
+        <v>-1.7372</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.8342</v>
+        <v>-1.2715</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3468</v>
+        <v>-0.4658</v>
       </c>
       <c r="J24" t="n">
-        <v>1.7685</v>
+        <v>-1.3213</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.1251</v>
+        <v>-1.3608</v>
       </c>
       <c r="L24" t="n">
-        <v>1.8937</v>
+        <v>0.0395</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.2559</v>
+        <v>-0.4159</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.7091</v>
+        <v>0.0893</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.5469</v>
+        <v>-0.5052</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.411</v>
+        <v>-0.6163999999999999</v>
       </c>
       <c r="Q24" t="n">
         <v>-2.0548</v>
       </c>
       <c r="R24" t="n">
-        <v>1.6439</v>
+        <v>1.4384</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0022</v>
+        <v>0.2007</v>
       </c>
       <c r="T24" t="n">
-        <v>0.8618</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.864</v>
+        <v>0.1283</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.2397</v>
+        <v>-0.0479</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.2397</v>
+        <v>-0.0479</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>R. DIAZ DEL VALLE</t>
+          <t>T. PIERRE PHILIPPE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2463,67 +2463,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.2009</v>
+        <v>-4.5687</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.3037</v>
+        <v>-3.2685</v>
       </c>
       <c r="F25" t="n">
-        <v>1.1028</v>
+        <v>-1.3002</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.7372</v>
+        <v>-4.0018</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.2715</v>
+        <v>-2.4408</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4658</v>
+        <v>-1.561</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.3213</v>
+        <v>-2.4763</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.3608</v>
+        <v>-1.1366</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0395</v>
+        <v>-1.3396</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.4159</v>
+        <v>-1.5255</v>
       </c>
       <c r="N25" t="n">
-        <v>0.0893</v>
+        <v>-1.3041</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.5052</v>
+        <v>-0.2214</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.6163999999999999</v>
+        <v>0.2055</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.0548</v>
+        <v>-1.0274</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4384</v>
+        <v>1.2329</v>
       </c>
       <c r="S25" t="n">
-        <v>0.2007</v>
+        <v>-0.2532</v>
       </c>
       <c r="T25" t="n">
-        <v>0.07240000000000001</v>
+        <v>-0.0045</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1283</v>
+        <v>-0.2487</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.0479</v>
+        <v>-0.5192</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>0.2397</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.0479</v>
+        <v>-0.7589</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>T. PIERRE PHILIPPE</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2546,152 +2546,69 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.5687</v>
+        <v>-2.701199999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.2685</v>
+        <v>5.799099999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.3002</v>
+        <v>-8.500400000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>-4.0018</v>
+        <v>-10.775</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.4408</v>
+        <v>-7.071199999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.561</v>
+        <v>-3.7039</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.4763</v>
+        <v>12.7679</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.1366</v>
+        <v>5.2606</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.3396</v>
+        <v>7.507400000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.5255</v>
+        <v>-23.5428</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.3041</v>
+        <v>-12.3318</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.2214</v>
+        <v>-11.2112</v>
       </c>
       <c r="P26" t="n">
-        <v>0.2055</v>
+        <v>3.082199999999999</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.0274</v>
+        <v>-15.411</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2329</v>
+        <v>18.4934</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.2532</v>
+        <v>1.5667</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.0045</v>
+        <v>3.798499999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2487</v>
+        <v>-2.2317</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.5192</v>
+        <v>3.424699999999999</v>
       </c>
       <c r="W26" t="n">
-        <v>0.2397</v>
+        <v>4.6437</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.7589</v>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>play_by_play_2536302_LIGAREGULARB_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>AMICS CASTELLÓ</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" t="n">
-        <v>-2.701199999999999</v>
-      </c>
-      <c r="E27" t="n">
-        <v>5.799099999999999</v>
-      </c>
-      <c r="F27" t="n">
-        <v>-8.500400000000001</v>
-      </c>
-      <c r="G27" t="n">
-        <v>-10.775</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-7.071199999999999</v>
-      </c>
-      <c r="I27" t="n">
-        <v>-3.7038</v>
-      </c>
-      <c r="J27" t="n">
-        <v>12.7679</v>
-      </c>
-      <c r="K27" t="n">
-        <v>5.2606</v>
-      </c>
-      <c r="L27" t="n">
-        <v>7.507500000000001</v>
-      </c>
-      <c r="M27" t="n">
-        <v>-23.5428</v>
-      </c>
-      <c r="N27" t="n">
-        <v>-12.3318</v>
-      </c>
-      <c r="O27" t="n">
-        <v>-11.2112</v>
-      </c>
-      <c r="P27" t="n">
-        <v>3.082199999999999</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>-15.411</v>
-      </c>
-      <c r="R27" t="n">
-        <v>18.4934</v>
-      </c>
-      <c r="S27" t="n">
-        <v>1.5667</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3.798499999999999</v>
-      </c>
-      <c r="U27" t="n">
-        <v>-2.2317</v>
-      </c>
-      <c r="V27" t="n">
-        <v>3.424699999999999</v>
-      </c>
-      <c r="W27" t="n">
-        <v>4.6437</v>
-      </c>
-      <c r="X27" t="n">
         <v>-1.2191</v>
       </c>
-      <c r="Y27" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
